--- a/artfynd/A 28001-2023 artfynd.xlsx
+++ b/artfynd/A 28001-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 28001-2023 artfynd.xlsx
+++ b/artfynd/A 28001-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96450097</v>
+        <v>111943947</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,45 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skidspåret, Storuman, Ly lm</t>
+          <t>Naturskogar Sorsele/Storuman, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600379.9580739464</v>
+        <v>600352</v>
       </c>
       <c r="R2" t="n">
-        <v>7221427.834951136</v>
+        <v>7221402</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-10-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-10-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Björn Ferry</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Björn Ferry</t>
+          <t>Maja Östlund, Simon Mattsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111943940</v>
+        <v>111943803</v>
       </c>
       <c r="B3" t="n">
-        <v>77650</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600237</v>
+        <v>600424</v>
       </c>
       <c r="R3" t="n">
-        <v>7221447</v>
+        <v>7221684</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -890,44 +862,39 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maja Östlund, Simon Mattsson</t>
+          <t>Simon Mattsson, Maja Östlund</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111943877</v>
+        <v>111943814</v>
       </c>
       <c r="B4" t="n">
-        <v>90814</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600476</v>
+        <v>600437</v>
       </c>
       <c r="R4" t="n">
-        <v>7221499</v>
+        <v>7221630</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1002,16 +969,11 @@
         <v>111943815</v>
       </c>
       <c r="B5" t="n">
-        <v>90830</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1101,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111943803</v>
+        <v>111943816</v>
       </c>
       <c r="B6" t="n">
-        <v>89553</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>2059</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600424</v>
+        <v>600428</v>
       </c>
       <c r="R6" t="n">
-        <v>7221684</v>
+        <v>7221623</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1203,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111943841</v>
+        <v>111943907</v>
       </c>
       <c r="B7" t="n">
-        <v>77403</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600367</v>
+        <v>600409</v>
       </c>
       <c r="R7" t="n">
-        <v>7221297</v>
+        <v>7221648</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1298,7 +1250,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Maja Östlund</t>
+          <t>Maja Östlund, Simon Mattsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1308,12 +1260,7 @@
         <v>111943887</v>
       </c>
       <c r="B8" t="n">
-        <v>90808</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,19 +1354,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111943881</v>
+        <v>111943877</v>
       </c>
       <c r="B9" t="n">
-        <v>90814</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1447,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600419</v>
+        <v>600476</v>
       </c>
       <c r="R9" t="n">
-        <v>7221630</v>
+        <v>7221499</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1509,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111943816</v>
+        <v>111943879</v>
       </c>
       <c r="B10" t="n">
-        <v>90830</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1525,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1549,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600428</v>
+        <v>600452</v>
       </c>
       <c r="R10" t="n">
-        <v>7221623</v>
+        <v>7221545</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1611,19 +1548,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111943944</v>
+        <v>111943880</v>
       </c>
       <c r="B11" t="n">
-        <v>90814</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1651,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600345</v>
+        <v>600438</v>
       </c>
       <c r="R11" t="n">
-        <v>7221526</v>
+        <v>7221453</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1706,26 +1638,21 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Maja Östlund, Simon Mattsson</t>
+          <t>Simon Mattsson, Maja Östlund</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111943882</v>
+        <v>111943881</v>
       </c>
       <c r="B12" t="n">
-        <v>90814</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1756,7 +1683,7 @@
         <v>600419</v>
       </c>
       <c r="R12" t="n">
-        <v>7221432</v>
+        <v>7221630</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1815,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111943947</v>
+        <v>111943882</v>
       </c>
       <c r="B13" t="n">
-        <v>85850</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1831,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>510</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1855,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600352</v>
+        <v>600419</v>
       </c>
       <c r="R13" t="n">
-        <v>7221402</v>
+        <v>7221432</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1910,22 +1832,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Maja Östlund, Simon Mattsson</t>
+          <t>Simon Mattsson, Maja Östlund</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111943814</v>
+        <v>111943883</v>
       </c>
       <c r="B14" t="n">
-        <v>90830</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1933,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1957,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>600437</v>
+        <v>600311</v>
       </c>
       <c r="R14" t="n">
-        <v>7221630</v>
+        <v>7221358</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2019,19 +1936,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111943880</v>
+        <v>111943944</v>
       </c>
       <c r="B15" t="n">
-        <v>90814</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2059,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600437</v>
+        <v>600346</v>
       </c>
       <c r="R15" t="n">
-        <v>7221453</v>
+        <v>7221526</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2114,44 +2026,39 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Maja Östlund</t>
+          <t>Maja Östlund, Simon Mattsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111943883</v>
+        <v>111943940</v>
       </c>
       <c r="B16" t="n">
-        <v>90814</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2161,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>600311</v>
+        <v>600236</v>
       </c>
       <c r="R16" t="n">
-        <v>7221358</v>
+        <v>7221447</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2216,22 +2123,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Maja Östlund</t>
+          <t>Maja Östlund, Simon Mattsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111943879</v>
+        <v>96450088</v>
       </c>
       <c r="B17" t="n">
-        <v>90814</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2239,37 +2141,49 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Naturskogar Sorsele/Storuman, Ly lm</t>
+          <t>Skidspåret, Storuman, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>600452</v>
+        <v>600380</v>
       </c>
       <c r="R17" t="n">
-        <v>7221545</v>
+        <v>7221427</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2293,12 +2207,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2021-10-04</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2021-10-04</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Sprang en runda på skidspåret och hörde spillkråkans lockrop - kly-äää- från andra sidan 45:an.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2313,27 +2242,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Björn Ferry</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Maja Östlund</t>
+          <t>Björn Ferry</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111943907</v>
+        <v>111943841</v>
       </c>
       <c r="B18" t="n">
-        <v>90830</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2341,21 +2265,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2059</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2365,10 +2289,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>600409</v>
+        <v>600367</v>
       </c>
       <c r="R18" t="n">
-        <v>7221648</v>
+        <v>7221298</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2420,7 +2344,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Maja Östlund, Simon Mattsson</t>
+          <t>Simon Mattsson, Maja Östlund</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 28001-2023 artfynd.xlsx
+++ b/artfynd/A 28001-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111943803</v>
+        <v>135326932</v>
       </c>
       <c r="B3" t="n">
-        <v>91909</v>
+        <v>89354</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Naturskogar Sorsele/Storuman, Ly lm</t>
+          <t>Storuman C, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600424</v>
+        <v>600358</v>
       </c>
       <c r="R3" t="n">
-        <v>7221684</v>
+        <v>7221402</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -837,12 +837,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,44 +867,48 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Maja Östlund</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111943814</v>
+        <v>111943803</v>
       </c>
       <c r="B4" t="n">
-        <v>93213</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2059</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600437</v>
+        <v>600424</v>
       </c>
       <c r="R4" t="n">
-        <v>7221630</v>
+        <v>7221684</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -966,48 +980,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111943815</v>
+        <v>135326893</v>
       </c>
       <c r="B5" t="n">
-        <v>93213</v>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2059</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Naturskogar Sorsele/Storuman, Ly lm</t>
+          <t>Storuman C, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600430</v>
+        <v>600590</v>
       </c>
       <c r="R5" t="n">
-        <v>7221629</v>
+        <v>7221690</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1031,12 +1045,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1051,60 +1075,64 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Maja Östlund</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111943816</v>
+        <v>135326895</v>
       </c>
       <c r="B6" t="n">
-        <v>93213</v>
+        <v>91974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2059</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Naturskogar Sorsele/Storuman, Ly lm</t>
+          <t>Storuman C, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600428</v>
+        <v>600580</v>
       </c>
       <c r="R6" t="n">
-        <v>7221623</v>
+        <v>7221677</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1128,12 +1156,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1148,60 +1186,64 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Maja Östlund</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111943907</v>
+        <v>135326944</v>
       </c>
       <c r="B7" t="n">
-        <v>93213</v>
+        <v>91974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2059</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Naturskogar Sorsele/Storuman, Ly lm</t>
+          <t>Storuman C, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600409</v>
+        <v>600289</v>
       </c>
       <c r="R7" t="n">
-        <v>7221648</v>
+        <v>7221547</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1225,12 +1267,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1245,22 +1297,26 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Maja Östlund, Simon Mattsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111943887</v>
+        <v>135326959</v>
       </c>
       <c r="B8" t="n">
-        <v>93191</v>
+        <v>91974</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,37 +1324,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Naturskogar Sorsele/Storuman, Ly lm</t>
+          <t>Storuman C, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600485</v>
+        <v>600504</v>
       </c>
       <c r="R8" t="n">
-        <v>7221470</v>
+        <v>7221683</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1322,12 +1378,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1342,44 +1408,48 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Maja Östlund</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111943877</v>
+        <v>111943814</v>
       </c>
       <c r="B9" t="n">
-        <v>93197</v>
+        <v>93213</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600476</v>
+        <v>600437</v>
       </c>
       <c r="R9" t="n">
-        <v>7221499</v>
+        <v>7221630</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1451,32 +1521,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111943879</v>
+        <v>111943815</v>
       </c>
       <c r="B10" t="n">
-        <v>93197</v>
+        <v>93213</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600452</v>
+        <v>600430</v>
       </c>
       <c r="R10" t="n">
-        <v>7221545</v>
+        <v>7221629</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1548,32 +1618,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111943880</v>
+        <v>111943816</v>
       </c>
       <c r="B11" t="n">
-        <v>93197</v>
+        <v>93213</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600438</v>
+        <v>600428</v>
       </c>
       <c r="R11" t="n">
-        <v>7221453</v>
+        <v>7221623</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1645,32 +1715,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111943881</v>
+        <v>111943907</v>
       </c>
       <c r="B12" t="n">
-        <v>93197</v>
+        <v>93213</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600419</v>
+        <v>600409</v>
       </c>
       <c r="R12" t="n">
-        <v>7221630</v>
+        <v>7221648</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1735,17 +1805,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Maja Östlund</t>
+          <t>Maja Östlund, Simon Mattsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111943882</v>
+        <v>111943887</v>
       </c>
       <c r="B13" t="n">
-        <v>93197</v>
+        <v>93191</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1823,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600419</v>
+        <v>600485</v>
       </c>
       <c r="R13" t="n">
-        <v>7221432</v>
+        <v>7221470</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1839,7 +1909,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111943883</v>
+        <v>111943877</v>
       </c>
       <c r="B14" t="n">
         <v>93197</v>
@@ -1874,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>600311</v>
+        <v>600476</v>
       </c>
       <c r="R14" t="n">
-        <v>7221358</v>
+        <v>7221499</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1936,7 +2006,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111943944</v>
+        <v>111943879</v>
       </c>
       <c r="B15" t="n">
         <v>93197</v>
@@ -1971,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600346</v>
+        <v>600452</v>
       </c>
       <c r="R15" t="n">
-        <v>7221526</v>
+        <v>7221545</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2026,39 +2096,39 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Maja Östlund, Simon Mattsson</t>
+          <t>Simon Mattsson, Maja Östlund</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111943940</v>
+        <v>111943880</v>
       </c>
       <c r="B16" t="n">
-        <v>79327</v>
+        <v>93197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2138,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>600236</v>
+        <v>600438</v>
       </c>
       <c r="R16" t="n">
-        <v>7221447</v>
+        <v>7221453</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2123,67 +2193,55 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Maja Östlund, Simon Mattsson</t>
+          <t>Simon Mattsson, Maja Östlund</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>96450088</v>
+        <v>111943881</v>
       </c>
       <c r="B17" t="n">
-        <v>57950</v>
+        <v>93197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skidspåret, Storuman, Ly lm</t>
+          <t>Naturskogar Sorsele/Storuman, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>600380</v>
+        <v>600419</v>
       </c>
       <c r="R17" t="n">
-        <v>7221427</v>
+        <v>7221630</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2207,27 +2265,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-10-04</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-10-04</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Sprang en runda på skidspåret och hörde spillkråkans lockrop - kly-äää- från andra sidan 45:an.</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2242,22 +2285,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Björn Ferry</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Björn Ferry</t>
+          <t>Simon Mattsson, Maja Östlund</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111943841</v>
+        <v>111943882</v>
       </c>
       <c r="B18" t="n">
-        <v>79085</v>
+        <v>93197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2265,21 +2308,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2289,10 +2332,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>600367</v>
+        <v>600419</v>
       </c>
       <c r="R18" t="n">
-        <v>7221298</v>
+        <v>7221432</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2348,6 +2391,5903 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>111943883</v>
+      </c>
+      <c r="B19" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Naturskogar Sorsele/Storuman, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>600311</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7221358</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Simon Mattsson, Maja Östlund</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>111943944</v>
+      </c>
+      <c r="B20" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Naturskogar Sorsele/Storuman, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>600346</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7221526</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Maja Östlund, Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>111943940</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Naturskogar Sorsele/Storuman, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>600236</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7221447</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Maja Östlund, Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135326891</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>600617</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7221687</v>
+      </c>
+      <c r="S22" t="n">
+        <v>11</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135326896</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>600563</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7221679</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135326906</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>600588</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7221642</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Gott om</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135326924</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>600268</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7221374</v>
+      </c>
+      <c r="S25" t="n">
+        <v>77</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135326930</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>600301</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7221432</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135326943</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>600298</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7221517</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135326951</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>600250</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7221526</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135326958</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>600495</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7221690</v>
+      </c>
+      <c r="S29" t="n">
+        <v>13</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>96450088</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Skidspåret, Storuman, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>600380</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7221427</v>
+      </c>
+      <c r="S30" t="n">
+        <v>50</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2021-10-04</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2021-10-04</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Sprang en runda på skidspåret och hörde spillkråkans lockrop - kly-äää- från andra sidan 45:an.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Björn Ferry</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Björn Ferry</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135326894</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>600583</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7221674</v>
+      </c>
+      <c r="S31" t="n">
+        <v>32</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135326892</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>600581</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7221690</v>
+      </c>
+      <c r="S32" t="n">
+        <v>12</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Skalad klen gran</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135326899</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>600594</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7221682</v>
+      </c>
+      <c r="S33" t="n">
+        <v>14</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Påbörjade ringhack och skalat på samma gran</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135326900</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>600600</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7221658</v>
+      </c>
+      <c r="S34" t="n">
+        <v>20</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Skalad granlåga</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135326904</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>600586</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7221639</v>
+      </c>
+      <c r="S35" t="n">
+        <v>9</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Skalad klenare gran</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135326910</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>600612</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7221622</v>
+      </c>
+      <c r="S36" t="n">
+        <v>17</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Litegrann skalat på underveg gran.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135326911</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>600589</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7221608</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Svagt men troligt påbörjat ringhack 4-6 m upp i tall</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135326920</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>600464</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7221338</v>
+      </c>
+      <c r="S38" t="n">
+        <v>22</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack. Bara en ring men färskt med rinnande kåda</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135326925</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>600272</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7221340</v>
+      </c>
+      <c r="S39" t="n">
+        <v>20</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Skalad död gran</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135326928</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>600286</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7221403</v>
+      </c>
+      <c r="S40" t="n">
+        <v>11</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Skalade snöbrutna smågranar</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135326935</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>600369</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7221391</v>
+      </c>
+      <c r="S41" t="n">
+        <v>45</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färsk skalad underveggran</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135326936</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>600384</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7221409</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Skalad klen gran och även en tjockare</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135326939</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>600380</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7221430</v>
+      </c>
+      <c r="S43" t="n">
+        <v>87</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Klen skalad gran</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135326940</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>600362</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7221468</v>
+      </c>
+      <c r="S44" t="n">
+        <v>38</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Skalad klenare gran</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135326942</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>600322</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7221493</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Skalade stående döda granar</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135326945</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>600280</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7221565</v>
+      </c>
+      <c r="S46" t="n">
+        <v>12</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135326946</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>600280</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7221560</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack gran</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135326947</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>600278</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7221544</v>
+      </c>
+      <c r="S48" t="n">
+        <v>7</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack gran</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135326948</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>600242</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7221502</v>
+      </c>
+      <c r="S49" t="n">
+        <v>16</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135326949</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>600238</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7221493</v>
+      </c>
+      <c r="S50" t="n">
+        <v>13</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135326950</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>600224</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7221488</v>
+      </c>
+      <c r="S51" t="n">
+        <v>16</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135326952</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>600307</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7221597</v>
+      </c>
+      <c r="S52" t="n">
+        <v>16</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135326954</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>600371</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7221727</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack högt upp i tall</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135326955</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>600387</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7221723</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135326915</v>
+      </c>
+      <c r="B55" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>600496</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7221465</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Minst 2</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135326931</v>
+      </c>
+      <c r="B56" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>600315</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7221418</v>
+      </c>
+      <c r="S56" t="n">
+        <v>80</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135326938</v>
+      </c>
+      <c r="B57" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>600389</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7221414</v>
+      </c>
+      <c r="S57" t="n">
+        <v>24</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135326902</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>600577</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7221647</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>60+ blomställningar inom 2 meter diameter</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135326903</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>600582</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7221643</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>7 blommor och minimum 30 bladrosetter. 1 kvadratmeter</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135326905</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>600588</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7221643</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>21 blomställningar 1 kvadratmeter</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135326907</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>600604</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7221643</v>
+      </c>
+      <c r="S61" t="n">
+        <v>11</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>11 blomställningar</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135326960</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>600519</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7221692</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Minimum 33 blomställningar. Massa bladrosetter utan blommor. Ca 5 m diameter</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135326961</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>600544</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7221687</v>
+      </c>
+      <c r="S63" t="n">
+        <v>14</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Minst 17 blomställningar. Ca 4 m diameter</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135326962</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>600553</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7221687</v>
+      </c>
+      <c r="S64" t="n">
+        <v>14</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Minst 15 blomställningar. 2 kvm. Fler blad utan blommor än med</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>135326963</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>600505</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7221716</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>30+ bladrosetter på en kvm</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>135326964</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>600515</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7221728</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>8 blomställningar</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>111943841</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Naturskogar Sorsele/Storuman, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>600367</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7221298</v>
+      </c>
+      <c r="S67" t="n">
+        <v>20</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Simon Mattsson, Maja Östlund</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28001-2023 artfynd.xlsx
+++ b/artfynd/A 28001-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ18"/>
+  <dimension ref="A1:AZ67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111943803</v>
+        <v>135326932</v>
       </c>
       <c r="B3" t="n">
-        <v>91909</v>
+        <v>89426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Naturskogar Sorsele/Storuman, Ly lm</t>
+          <t>Storuman C, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600424</v>
+        <v>600358</v>
       </c>
       <c r="R3" t="n">
-        <v>7221684</v>
+        <v>7221402</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,49 +877,53 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Maja Östlund</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111943803</t>
+          <t>https://artportalen.se/Sighting/135326932</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111943814</v>
+        <v>111943803</v>
       </c>
       <c r="B4" t="n">
-        <v>93213</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2059</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600437</v>
+        <v>600424</v>
       </c>
       <c r="R4" t="n">
-        <v>7221630</v>
+        <v>7221684</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -980,54 +994,54 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111943814</t>
+          <t>https://artportalen.se/Sighting/111943803</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111943815</v>
+        <v>135326893</v>
       </c>
       <c r="B5" t="n">
-        <v>93213</v>
+        <v>92048</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2059</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Naturskogar Sorsele/Storuman, Ly lm</t>
+          <t>Storuman C, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600430</v>
+        <v>600590</v>
       </c>
       <c r="R5" t="n">
-        <v>7221629</v>
+        <v>7221690</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1065,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,65 +1095,69 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Maja Östlund</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111943815</t>
+          <t>https://artportalen.se/Sighting/135326893</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111943816</v>
+        <v>135326895</v>
       </c>
       <c r="B6" t="n">
-        <v>93213</v>
+        <v>92048</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2059</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Naturskogar Sorsele/Storuman, Ly lm</t>
+          <t>Storuman C, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600428</v>
+        <v>600580</v>
       </c>
       <c r="R6" t="n">
-        <v>7221623</v>
+        <v>7221677</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1153,12 +1181,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,65 +1211,69 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Maja Östlund</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111943816</t>
+          <t>https://artportalen.se/Sighting/135326895</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111943907</v>
+        <v>135326944</v>
       </c>
       <c r="B7" t="n">
-        <v>93213</v>
+        <v>92048</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2059</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Naturskogar Sorsele/Storuman, Ly lm</t>
+          <t>Storuman C, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600409</v>
+        <v>600289</v>
       </c>
       <c r="R7" t="n">
-        <v>7221648</v>
+        <v>7221547</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1255,12 +1297,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,27 +1327,31 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Maja Östlund, Simon Mattsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111943907</t>
+          <t>https://artportalen.se/Sighting/135326944</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111943887</v>
+        <v>135326959</v>
       </c>
       <c r="B8" t="n">
-        <v>93191</v>
+        <v>92048</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,37 +1359,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Naturskogar Sorsele/Storuman, Ly lm</t>
+          <t>Storuman C, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600485</v>
+        <v>600504</v>
       </c>
       <c r="R8" t="n">
-        <v>7221470</v>
+        <v>7221683</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1357,12 +1413,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1377,49 +1443,53 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Maja Östlund</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111943887</t>
+          <t>https://artportalen.se/Sighting/135326959</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111943877</v>
+        <v>111943814</v>
       </c>
       <c r="B9" t="n">
-        <v>93197</v>
+        <v>93213</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600476</v>
+        <v>600437</v>
       </c>
       <c r="R9" t="n">
-        <v>7221499</v>
+        <v>7221630</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1490,38 +1560,38 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111943877</t>
+          <t>https://artportalen.se/Sighting/111943814</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111943879</v>
+        <v>111943815</v>
       </c>
       <c r="B10" t="n">
-        <v>93197</v>
+        <v>93213</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600452</v>
+        <v>600430</v>
       </c>
       <c r="R10" t="n">
-        <v>7221545</v>
+        <v>7221629</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1592,38 +1662,38 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111943879</t>
+          <t>https://artportalen.se/Sighting/111943815</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111943880</v>
+        <v>111943816</v>
       </c>
       <c r="B11" t="n">
-        <v>93197</v>
+        <v>93213</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600438</v>
+        <v>600428</v>
       </c>
       <c r="R11" t="n">
-        <v>7221453</v>
+        <v>7221623</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1694,38 +1764,38 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111943880</t>
+          <t>https://artportalen.se/Sighting/111943816</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111943881</v>
+        <v>111943907</v>
       </c>
       <c r="B12" t="n">
-        <v>93197</v>
+        <v>93213</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600419</v>
+        <v>600409</v>
       </c>
       <c r="R12" t="n">
-        <v>7221630</v>
+        <v>7221648</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1790,22 +1860,22 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Maja Östlund</t>
+          <t>Maja Östlund, Simon Mattsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111943881</t>
+          <t>https://artportalen.se/Sighting/111943907</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111943882</v>
+        <v>111943887</v>
       </c>
       <c r="B13" t="n">
-        <v>93197</v>
+        <v>93191</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,21 +1883,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600419</v>
+        <v>600485</v>
       </c>
       <c r="R13" t="n">
-        <v>7221432</v>
+        <v>7221470</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1898,13 +1968,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111943882</t>
+          <t>https://artportalen.se/Sighting/111943887</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111943883</v>
+        <v>111943877</v>
       </c>
       <c r="B14" t="n">
         <v>93197</v>
@@ -1939,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>600311</v>
+        <v>600476</v>
       </c>
       <c r="R14" t="n">
-        <v>7221358</v>
+        <v>7221499</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2000,13 +2070,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111943883</t>
+          <t>https://artportalen.se/Sighting/111943877</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111943944</v>
+        <v>111943879</v>
       </c>
       <c r="B15" t="n">
         <v>93197</v>
@@ -2041,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600346</v>
+        <v>600452</v>
       </c>
       <c r="R15" t="n">
-        <v>7221526</v>
+        <v>7221545</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2096,44 +2166,44 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Maja Östlund, Simon Mattsson</t>
+          <t>Simon Mattsson, Maja Östlund</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111943944</t>
+          <t>https://artportalen.se/Sighting/111943879</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111943940</v>
+        <v>111943880</v>
       </c>
       <c r="B16" t="n">
-        <v>79327</v>
+        <v>93197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>600236</v>
+        <v>600438</v>
       </c>
       <c r="R16" t="n">
-        <v>7221447</v>
+        <v>7221453</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2198,72 +2268,60 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Maja Östlund, Simon Mattsson</t>
+          <t>Simon Mattsson, Maja Östlund</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111943940</t>
+          <t>https://artportalen.se/Sighting/111943880</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>96450088</v>
+        <v>111943881</v>
       </c>
       <c r="B17" t="n">
-        <v>57950</v>
+        <v>93197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skidspåret, Storuman, Ly lm</t>
+          <t>Naturskogar Sorsele/Storuman, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>600380</v>
+        <v>600419</v>
       </c>
       <c r="R17" t="n">
-        <v>7221427</v>
+        <v>7221630</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2287,27 +2345,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-10-04</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-10-04</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Sprang en runda på skidspåret och hörde spillkråkans lockrop - kly-äää- från andra sidan 45:an.</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2322,27 +2365,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Björn Ferry</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Björn Ferry</t>
+          <t>Simon Mattsson, Maja Östlund</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96450088</t>
+          <t>https://artportalen.se/Sighting/111943881</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111943841</v>
+        <v>111943882</v>
       </c>
       <c r="B18" t="n">
-        <v>79085</v>
+        <v>93197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2350,21 +2393,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2374,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>600367</v>
+        <v>600419</v>
       </c>
       <c r="R18" t="n">
-        <v>7221298</v>
+        <v>7221432</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2434,6 +2477,6148 @@
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111943882</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>111943883</v>
+      </c>
+      <c r="B19" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Naturskogar Sorsele/Storuman, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>600311</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7221358</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Simon Mattsson, Maja Östlund</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111943883</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>111943944</v>
+      </c>
+      <c r="B20" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Naturskogar Sorsele/Storuman, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>600346</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7221526</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Maja Östlund, Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111943944</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>111943940</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Naturskogar Sorsele/Storuman, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>600236</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7221447</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Maja Östlund, Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111943940</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135326891</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>600617</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7221687</v>
+      </c>
+      <c r="S22" t="n">
+        <v>11</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326891</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135326896</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>600563</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7221679</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326896</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135326906</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>600588</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7221642</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Gott om</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326906</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135326924</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>600268</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7221374</v>
+      </c>
+      <c r="S25" t="n">
+        <v>77</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326924</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135326930</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>600301</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7221432</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326930</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135326943</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>600298</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7221517</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326943</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135326951</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>600250</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7221526</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326951</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135326958</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>600495</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7221690</v>
+      </c>
+      <c r="S29" t="n">
+        <v>13</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326958</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>96450088</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Skidspåret, Storuman, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>600380</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7221427</v>
+      </c>
+      <c r="S30" t="n">
+        <v>50</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2021-10-04</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2021-10-04</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Sprang en runda på skidspåret och hörde spillkråkans lockrop - kly-äää- från andra sidan 45:an.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Björn Ferry</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Björn Ferry</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96450088</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135326894</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>600583</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7221674</v>
+      </c>
+      <c r="S31" t="n">
+        <v>32</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326894</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135326892</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>600581</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7221690</v>
+      </c>
+      <c r="S32" t="n">
+        <v>12</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Skalad klen gran</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326892</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135326899</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>600594</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7221682</v>
+      </c>
+      <c r="S33" t="n">
+        <v>14</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Påbörjade ringhack och skalat på samma gran</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326899</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135326900</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>600600</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7221658</v>
+      </c>
+      <c r="S34" t="n">
+        <v>20</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Skalad granlåga</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326900</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135326904</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>600586</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7221639</v>
+      </c>
+      <c r="S35" t="n">
+        <v>9</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Skalad klenare gran</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326904</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135326910</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>600612</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7221622</v>
+      </c>
+      <c r="S36" t="n">
+        <v>17</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Litegrann skalat på underveg gran.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326910</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135326911</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>600589</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7221608</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Svagt men troligt påbörjat ringhack 4-6 m upp i tall</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326911</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135326920</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>600464</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7221338</v>
+      </c>
+      <c r="S38" t="n">
+        <v>22</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack. Bara en ring men färskt med rinnande kåda</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326920</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135326925</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>600272</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7221340</v>
+      </c>
+      <c r="S39" t="n">
+        <v>20</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Skalad död gran</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326925</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135326928</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>600286</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7221403</v>
+      </c>
+      <c r="S40" t="n">
+        <v>11</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Skalade snöbrutna smågranar</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326928</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135326935</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>600369</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7221391</v>
+      </c>
+      <c r="S41" t="n">
+        <v>45</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färsk skalad underveggran</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326935</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135326936</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>600384</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7221409</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Skalad klen gran och även en tjockare</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326936</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135326939</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>600380</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7221430</v>
+      </c>
+      <c r="S43" t="n">
+        <v>87</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Klen skalad gran</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326939</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135326940</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>600362</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7221468</v>
+      </c>
+      <c r="S44" t="n">
+        <v>38</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Skalad klenare gran</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326940</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135326942</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>600322</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7221493</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Skalade stående döda granar</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326942</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135326945</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>600280</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7221565</v>
+      </c>
+      <c r="S46" t="n">
+        <v>12</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326945</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135326946</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>600280</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7221560</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack gran</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326946</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135326947</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>600278</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7221544</v>
+      </c>
+      <c r="S48" t="n">
+        <v>7</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack gran</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326947</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135326948</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>600242</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7221502</v>
+      </c>
+      <c r="S49" t="n">
+        <v>16</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326948</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135326949</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>600238</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7221493</v>
+      </c>
+      <c r="S50" t="n">
+        <v>13</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326949</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135326950</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>600224</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7221488</v>
+      </c>
+      <c r="S51" t="n">
+        <v>16</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326950</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135326952</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>600307</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7221597</v>
+      </c>
+      <c r="S52" t="n">
+        <v>16</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326952</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135326954</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>600371</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7221727</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack högt upp i tall</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326954</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135326955</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>600387</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7221723</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326955</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135326915</v>
+      </c>
+      <c r="B55" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>600496</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7221465</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Minst 2</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326915</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135326931</v>
+      </c>
+      <c r="B56" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>600315</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7221418</v>
+      </c>
+      <c r="S56" t="n">
+        <v>80</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326931</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135326938</v>
+      </c>
+      <c r="B57" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>600389</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7221414</v>
+      </c>
+      <c r="S57" t="n">
+        <v>24</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326938</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135326902</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>600577</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7221647</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>60+ blomställningar inom 2 meter diameter</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326902</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135326903</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>600582</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7221643</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>7 blommor och minimum 30 bladrosetter. 1 kvadratmeter</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326903</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135326905</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>600588</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7221643</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>21 blomställningar 1 kvadratmeter</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326905</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135326907</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>600604</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7221643</v>
+      </c>
+      <c r="S61" t="n">
+        <v>11</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>11 blomställningar</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326907</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135326960</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>600519</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7221692</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Minimum 33 blomställningar. Massa bladrosetter utan blommor. Ca 5 m diameter</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326960</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135326961</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>600544</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7221687</v>
+      </c>
+      <c r="S63" t="n">
+        <v>14</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Minst 17 blomställningar. Ca 4 m diameter</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326961</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135326962</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>600553</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7221687</v>
+      </c>
+      <c r="S64" t="n">
+        <v>14</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Minst 15 blomställningar. 2 kvm. Fler blad utan blommor än med</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326962</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>135326963</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>600505</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7221716</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>30+ bladrosetter på en kvm</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326963</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>135326964</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Storuman C, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>600515</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7221728</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>8 blomställningar</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326964</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>111943841</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Naturskogar Sorsele/Storuman, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>600367</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7221298</v>
+      </c>
+      <c r="S67" t="n">
+        <v>20</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Simon Mattsson, Maja Östlund</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/111943841</t>
         </is>
@@ -2458,6 +8643,55 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28001-2023 artfynd.xlsx
+++ b/artfynd/A 28001-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135326932</v>
       </c>
       <c r="B3" t="n">
-        <v>89426</v>
+        <v>89428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>135326893</v>
       </c>
       <c r="B5" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>135326895</v>
       </c>
       <c r="B6" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>135326944</v>
       </c>
       <c r="B7" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>135326959</v>
       </c>
       <c r="B8" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         <v>135326902</v>
       </c>
       <c r="B58" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>135326903</v>
       </c>
       <c r="B59" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
         <v>135326905</v>
       </c>
       <c r="B60" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>135326907</v>
       </c>
       <c r="B61" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>135326960</v>
       </c>
       <c r="B62" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>135326961</v>
       </c>
       <c r="B63" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>135326962</v>
       </c>
       <c r="B64" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>135326963</v>
       </c>
       <c r="B65" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8393,7 +8393,7 @@
         <v>135326964</v>
       </c>
       <c r="B66" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
